--- a/artfynd/A 13699-2024 artfynd.xlsx
+++ b/artfynd/A 13699-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114071397</v>
+        <v>114071393</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333718</v>
+        <v>333557</v>
       </c>
       <c r="R2" t="n">
-        <v>6433921</v>
+        <v>6434004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-01-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +772,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114071401</v>
+        <v>114271106</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedsåsen, Vg</t>
+          <t>Lödöse, Hedsåsen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333645</v>
+        <v>333674</v>
       </c>
       <c r="R3" t="n">
-        <v>6433994</v>
+        <v>6433883</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,17 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,33 +865,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114071393</v>
+        <v>114071396</v>
       </c>
       <c r="B4" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333557</v>
+        <v>333699</v>
       </c>
       <c r="R4" t="n">
-        <v>6434004</v>
+        <v>6433853</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-01-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,19 +986,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114071398</v>
+        <v>114071397</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>333626</v>
+        <v>333718</v>
       </c>
       <c r="R5" t="n">
-        <v>6433989</v>
+        <v>6433921</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,15 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114271106</v>
+        <v>114071398</v>
       </c>
       <c r="B6" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,41 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lödöse, Hedsåsen, Vg</t>
+          <t>Hedsåsen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>333674</v>
+        <v>333626</v>
       </c>
       <c r="R6" t="n">
-        <v>6433883</v>
+        <v>6433989</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,22 +1153,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-01-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,38 +1172,32 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114271181</v>
+        <v>114071401</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1249,23 +1219,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lödöse, Hedsåsen, Vg</t>
+          <t>Hedsåsen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>333784</v>
+        <v>333645</v>
       </c>
       <c r="R7" t="n">
-        <v>6433966</v>
+        <v>6433994</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1289,22 +1255,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-01-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,15 +1280,126 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114271181</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lödöse, Hedsåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>333784</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6433966</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13699-2024 artfynd.xlsx
+++ b/artfynd/A 13699-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114071393</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114271106</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114071396</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114071397</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114071398</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114071401</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,8 +1435,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114271181</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>